--- a/Trắc nghiệm ôn luyện/Embedded Software/multiple_choice_sample_template_RTOS_MULTITASKING.xlsx
+++ b/Trắc nghiệm ôn luyện/Embedded Software/multiple_choice_sample_template_RTOS_MULTITASKING.xlsx
@@ -453,19 +453,19 @@
         <v>Scheduler là hạt nhân của RTOS, chịu trách nhiệm quản lý trạng thái của các task và chuyển đổi quyền thực thi CPU dựa trên thuật toán lập lịch (thường là Preemptive scheduling dựa trên priority).</v>
       </c>
       <c r="E2" t="str">
+        <v>Mã hóa toàn bộ mã nguồn của file chạy binary trước khi nạp vào chip Flash — mã hóa tệp tin nạp</v>
+      </c>
+      <c r="F2" t="str">
         <v>Quyết định task nào có độ ưu tiên cao nhất đang sẵn sàng sẽ được cấp quyền CPU để chạy tiếp theo — bộ điều phối luồng chạy</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Tự động giải phóng dung lượng bộ nhớ RAM của vi điều khiển khi bị đầy — giải phóng bộ nhớ RAM</v>
       </c>
       <c r="G2" t="str">
         <v>Đọc tín hiệu điện áp từ chân ADC và chuyển đổi sang dạng số nguyên — đọc tín hiệu ngoại vi</v>
       </c>
       <c r="H2" t="str">
-        <v>Mã hóa toàn bộ mã nguồn của file chạy binary trước khi nạp vào chip Flash — mã hóa tệp tin nạp</v>
+        <v>Tự động giải phóng dung lượng bộ nhớ RAM của vi điều khiển khi bị đầy — giải phóng bộ nhớ RAM</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>Task ở trạng thái Blocked không tranh chấp CPU. Nó chỉ quay lại trạng thái Ready khi sự kiện nó chờ đợi được đáp ứng (ví dụ: hết thời gian delay hoặc nhận được semaphore).</v>
       </c>
       <c r="E3" t="str">
+        <v>Task đang trực tiếp sử dụng CPU để tính toán các thuật toán toán học — đang chạy thực tế</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Task đã bị xóa vĩnh viễn khỏi bộ nhớ của vi điều khiển và không thể gọi lại được — bị xóa khỏi RAM</v>
+      </c>
+      <c r="G3" t="str">
         <v>Task đang dừng chạy để đợi một sự kiện hoặc tài nguyên xảy ra (như Semaphore, Delay, Queue) — đợi sự kiện tài nguyên</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Task đang trực tiếp sử dụng CPU để tính toán các thuật toán toán học — đang chạy thực tế</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Task đã bị xóa vĩnh viễn khỏi bộ nhớ của vi điều khiển và không thể gọi lại được — bị xóa khỏi RAM</v>
       </c>
       <c r="H3" t="str">
         <v>Task đang bị lỗi cú pháp lập trình khiến hệ điều hành không biên dịch được — lỗi cú pháp mã nguồn</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         <v>Semaphore (như Binary Semaphore) — cơ chế phát tín hiệu đồng bộ hóa gọn nhẹ — phát tín hiệu đồng bộ</v>
       </c>
       <c r="F4" t="str">
-        <v>Mutex (Mutual Exclusion) — cơ chế khóa độc quyền có hỗ trợ kế thừa độ ưu tiên — khóa loại trừ tương hỗ</v>
+        <v>Dynamic Memory Allocation (Cấp phát động malloc/free) — cấp phát động bộ nhớ heap</v>
       </c>
       <c r="G4" t="str">
         <v>Global Variable (Biến toàn cục thông thường) không khai báo volatile — biến thường không an toàn ngắt</v>
       </c>
       <c r="H4" t="str">
-        <v>Dynamic Memory Allocation (Cấp phát động malloc/free) — cấp phát động bộ nhớ heap</v>
+        <v>Mutex (Mutual Exclusion) — cơ chế khóa độc quyền có hỗ trợ kế thừa độ ưu tiên — khóa loại trừ tương hỗ</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -540,7 +540,7 @@
         <v>Vòng lặp trễ (busy waiting) làm lãng phí năng lượng và tài nguyên CPU. `vTaskDelay()` cho phép RTOS chuyển ngữ cảnh sang task Ready khác, tối ưu hóa đa nhiệm.</v>
       </c>
       <c r="E5" t="str">
-        <v>Vì `vTaskDelay()` đưa task hiện tại vào trạng thái Blocked để nhường CPU cho các task khác chạy; vòng lặp trễ chiếm dụng 100% CPU vô ích — giải phóng CPU cho task khác</v>
+        <v>Vì hàm này chỉ chạy được trên các dòng vi điều khiển 8-bit giá rẻ — giới hạn phần cứng chip</v>
       </c>
       <c r="F5" t="str">
         <v>Vì `vTaskDelay()` tự động khóa toàn bộ các ngắt toàn cục của vi điều khiển — khóa ngắt toàn cục</v>
@@ -549,10 +549,10 @@
         <v>Vì `vTaskDelay()` giúp vi điều khiển chạy nhanh gấp 10 lần so với bình thường — tăng tốc độ chip</v>
       </c>
       <c r="H5" t="str">
-        <v>Vì hàm này chỉ chạy được trên các dòng vi điều khiển 8-bit giá rẻ — giới hạn phần cứng chip</v>
+        <v>Vì `vTaskDelay()` đưa task hiện tại vào trạng thái Blocked để nhường CPU cho các task khác chạy; vòng lặp trễ chiếm dụng 100% CPU vô ích — giải phóng CPU cho task khác</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -575,10 +575,10 @@
         <v>Độ ưu tiên của task đó so với các task khác trong hệ thống — độ ưu tiên của task</v>
       </c>
       <c r="G6" t="str">
+        <v>Số lượng các biến toàn cục mà task được phép truy cập trong chương trình — giới hạn truy cập biến</v>
+      </c>
+      <c r="H6" t="str">
         <v>Thời gian tối đa task được phép chiếm dụng CPU trong một chu kỳ lập lịch — khung thời gian chạy</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Số lượng các biến toàn cục mà task được phép truy cập trong chương trình — giới hạn truy cập biến</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -598,19 +598,19 @@
         <v>Message Queue cho phép gửi các bản tin (struct, con trỏ dữ liệu) giữa các luồng chạy độc lập một cách an toàn, tránh lỗi xung đột tranh chấp bộ nhớ (Race Condition).</v>
       </c>
       <c r="E7" t="str">
+        <v>Lưu trữ mã nguồn code dưới dạng tệp tin nén zip trên bộ nhớ Flash của chip — lưu trữ mã nguồn</v>
+      </c>
+      <c r="F7" t="str">
         <v>Truyền và trao đổi dữ liệu an toàn giữa các tasks hoặc giữa ISR và tasks theo cơ chế hàng đợi FIFO — truyền dữ liệu đa nhiệm an toàn</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Tự động gửi tin nhắn SMS báo cáo trạng thái của chip về điện thoại của lập trình viên — gửi tin nhắn SMS</v>
       </c>
       <c r="G7" t="str">
         <v>Đo lường thời gian trễ của đường truyền internet kết nối vào vi điều khiển — đo lường độ trễ mạng</v>
       </c>
       <c r="H7" t="str">
-        <v>Lưu trữ mã nguồn code dưới dạng tệp tin nén zip trên bộ nhớ Flash của chip — lưu trữ mã nguồn</v>
+        <v>Tự động gửi tin nhắn SMS báo cáo trạng thái của chip về điện thoại của lập trình viên — gửi tin nhắn SMS</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Context Switching bao gồm việc lưu các thanh ghi CPU của task cũ vào stack của nó, cập nhật con trỏ stack, và nạp lại các thanh ghi CPU từ stack của task mới để bắt đầu thực thi.</v>
       </c>
       <c r="E8" t="str">
-        <v>Quá trình lưu lại trạng thái CPU của task đang chạy và khôi phục trạng thái CPU của task tiếp theo để thực thi — chuyển đổi trạng thái CPU</v>
+        <v>Quá trình thay đổi ngôn ngữ lập trình của dự án từ C sang C++ — thay đổi ngôn ngữ code</v>
       </c>
       <c r="F8" t="str">
         <v>Quá trình nạp lại firmware mới cho vi điều khiển thông qua cổng nạp SWD — nạp lại firmware mới</v>
       </c>
       <c r="G8" t="str">
+        <v>Quá trình lưu lại trạng thái CPU của task đang chạy và khôi phục trạng thái CPU của task tiếp theo để thực thi — chuyển đổi trạng thái CPU</v>
+      </c>
+      <c r="H8" t="str">
         <v>Quá trình chuyển đổi tín hiệu từ dạng tương tự (Analog) sang dạng số (Digital) — chuyển đổi tín hiệu ADC</v>
       </c>
-      <c r="H8" t="str">
-        <v>Quá trình thay đổi ngôn ngữ lập trình của dự án từ C sang C++ — thay đổi ngôn ngữ code</v>
-      </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>Sau khi đã khai báo các task, queue, semaphore trong hàm `main()`, ta gọi `vTaskStartScheduler()` để trao quyền điều phối CPU hoàn toàn cho RTOS.</v>
       </c>
       <c r="E9" t="str">
+        <v>vTaskDelay() — dùng để đưa task vào trạng thái delay tạm thời — trì hoãn task</v>
+      </c>
+      <c r="F9" t="str">
         <v>vTaskStartScheduler() — bắt đầu khởi chạy hệ điều hành thời gian thực — khởi chạy scheduler</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>xTaskCreate() — dùng để khai báo và tạo một task mới trong hệ thống — tạo task mới</v>
-      </c>
-      <c r="G9" t="str">
-        <v>vTaskDelay() — dùng để đưa task vào trạng thái delay tạm thời — trì hoãn task</v>
       </c>
       <c r="H9" t="str">
         <v>taskYIELD() — dùng để nhường quyền CPU chủ động cho task khác có cùng priority — nhường quyền CPU</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>Mutex (Mutual Exclusion) dùng để bảo vệ tài nguyên dùng chung (Shared Resource). Nó có cơ chế "mượn khóa" (Ownership). Chỉ task đang giữ Mutex mới giải phóng được nó. Semaphore dùng để đồng bộ hóa (signaling): Task A tạo ra sự kiện thì nhả semaphore để Task B nhận và chạy.</v>
       </c>
       <c r="E10" t="str">
-        <v>Mutex có khái niệm sở hữu (Ownership - chỉ task khóa mới được mở) và hỗ trợ giải quyết Priority Inversion; Binary Semaphore không có owner, chuyên dùng cho signaling — sở hữu &amp; chống nghịch đảo ưu tiên vs phát tín hiệu</v>
+        <v>Mutex bắt buộc phải lưu trong bộ nhớ Flash; còn Binary Semaphore lưu trong bộ nhớ RAM — phân loại phân vùng bộ nhớ</v>
       </c>
       <c r="F10" t="str">
         <v>Mutex chỉ dùng cho lập trình nhúng 32-bit; Binary Semaphore chỉ dùng cho lập trình nhúng 8-bit — phân loại theo bit vi điều khiển</v>
       </c>
       <c r="G10" t="str">
-        <v>Mutex bắt buộc phải lưu trong bộ nhớ Flash; còn Binary Semaphore lưu trong bộ nhớ RAM — phân loại phân vùng bộ nhớ</v>
+        <v>Mutex có khái niệm sở hữu (Ownership - chỉ task khóa mới được mở) và hỗ trợ giải quyết Priority Inversion; Binary Semaphore không có owner, chuyên dùng cho signaling — sở hữu &amp; chống nghịch đảo ưu tiên vs phát tín hiệu</v>
       </c>
       <c r="H10" t="str">
         <v>Mutex chạy nhanh gấp 10 lần so với Binary Semaphore do không sử dụng cơ chế hàng đợi — so sánh hiệu năng chạy</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Priority Inversion là lỗi thiết kế kinh điển (từng làm tê liệt robot tự hành Mars Pathfinder). Task Cao bị chặn bởi Task Thấp (do dùng chung khóa). Nhưng Task Trung bình không cần khóa lại nhảy vào cướp CPU của Task Thấp, làm Task Thấp không thể chạy để trả khóa cho Task Cao, gián tiếp làm Task Cao bị block lâu hơn cả Task Trung bình.</v>
       </c>
       <c r="E11" t="str">
+        <v>Vi điều khiển bị quá nhiệt khiến hệ điều hành hoạt động sai lệch logic lập lịch — vi điều khiển quá nhiệt</v>
+      </c>
+      <c r="F11" t="str">
         <v>Task độ ưu tiên cao bị block để đợi tài nguyên giữ bởi task độ ưu tiên thấp, trong khi một task độ ưu tiên trung bình nhảy vào chiếm CPU cản trở task thấp nhả tài nguyên — task trung bình cản trở task cao</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>Hệ điều hành tự động đảo ngược độ ưu tiên của tất cả các task sau mỗi 10 mili-giây — tự động đảo độ ưu tiên</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Lập trình viên vô ý khai báo sai số thứ tự độ ưu tiên của các task trong hàm main() — lỗi khai báo nhầm lẫn</v>
       </c>
-      <c r="H11" t="str">
-        <v>Vi điều khiển bị quá nhiệt khiến hệ điều hành hoạt động sai lệch logic lập lịch — vi điều khiển quá nhiệt</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Khi nâng tạm thời priority của Task Thấp lên bằng Task Cao, các Task Trung bình sẽ không thể cướp CPU của nó được nữa. Task Thấp sẽ nhanh chóng hoàn thành vùng găng (Critical Section) để nhả Mutex cho Task Cao.</v>
       </c>
       <c r="E12" t="str">
+        <v>Ngắt toàn bộ các yêu cầu xử lý của CPU để tập trung chạy lại từ đầu hệ điều hành — reset hệ điều hành</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Tạo ra một bản sao khóa phụ để cấp phát cho Task cao cùng sử dụng chung tài nguyên — tạo khóa phụ song song</v>
+      </c>
+      <c r="G12" t="str">
         <v>Tạm thời nâng độ ưu tiên của Task thấp (đang giữ khóa) lên bằng độ ưu tiên của Task cao (đang đợi khóa) để nó chạy nhanh và trả khóa, sau đó trả về độ ưu tiên cũ — nâng ưu tiên tạm thời để trả khóa</v>
       </c>
-      <c r="F12" t="str">
+      <c r="H12" t="str">
         <v>Tự động xóa bỏ Task trung bình ra khỏi bộ nhớ của hệ thống khi có tranh chấp xảy ra — xóa task trung bình</v>
       </c>
-      <c r="G12" t="str">
-        <v>Tạo ra một bản sao khóa phụ để cấp phát cho Task cao cùng sử dụng chung tài nguyên — tạo khóa phụ song song</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Ngắt toàn bộ các yêu cầu xử lý của CPU để tập trung chạy lại từ đầu hệ điều hành — reset hệ điều hành</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -772,7 +772,7 @@
         <v>ISR cần thực thi cực nhanh và không được phép bị chặn (Blocked). Các API RTOS thông thường có cơ chế block/timeout nếu tài nguyên chưa sẵn sàng. Phiên bản `FromISR` không bao giờ bị block, đảm bảo tính an toàn cho ngắt.</v>
       </c>
       <c r="E13" t="str">
-        <v>Vì API thường có thể gây block/delay hệ thống, làm treo tiến trình ISR; khắc phục bằng cách sử dụng các API chuyên biệt cho ngắt có hậu tố "FromISR" (như `xSemaphoreGiveFromISR()`) — tránh gây block trong ngắt sử dụng API FromISR</v>
+        <v>Khắc phục bằng cách viết code ngắt hoàn toàn bằng ngôn ngữ Assembly thay vì C nhúng — viết code Assembly</v>
       </c>
       <c r="F13" t="str">
         <v>Vì gọi API thường trong ngắt sẽ làm sập nguồn điện của vi điều khiển ngay lập tức — sập nguồn điện chip</v>
@@ -781,10 +781,10 @@
         <v>Vì ISR chỉ hỗ trợ đọc dữ liệu chứ không cho phép thực hiện bất kỳ phép toán logic nào — giới hạn tính năng ISR</v>
       </c>
       <c r="H13" t="str">
-        <v>Khắc phục bằng cách viết code ngắt hoàn toàn bằng ngôn ngữ Assembly thay vì C nhúng — viết code Assembly</v>
+        <v>Vì API thường có thể gây block/delay hệ thống, làm treo tiến trình ISR; khắc phục bằng cách sử dụng các API chuyên biệt cho ngắt có hậu tố "FromISR" (như `xSemaphoreGiveFromISR()`) — tránh gây block trong ngắt sử dụng API FromISR</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -801,7 +801,7 @@
         <v>Idle Task có priority thấp nhất (0). Khi CPU rảnh rỗi (không có việc gì làm), Idle Task sẽ chạy. Đây là nơi lý tưởng để cấu hình chip ngủ (Sleep Mode) nhằm tiết kiệm năng lượng cho các thiết bị chạy pin.</v>
       </c>
       <c r="E14" t="str">
-        <v>Là task tự động chạy khi không có task nào khác ở trạng thái Ready, thường dùng để đưa chip vào chế độ tiết kiệm năng lượng (Low-power/Sleep) — chạy khi rảnh tiết kiệm điện năng</v>
+        <v>Là task tự động xóa toàn bộ các tệp tin log rác lưu trữ trên bộ nhớ ngoài Flash — dọn dẹp bộ nhớ Flash</v>
       </c>
       <c r="F14" t="str">
         <v>Là task có độ ưu tiên cao nhất hệ thống, dùng để giám sát và tiêu diệt các task bị treo — giám sát hệ thống</v>
@@ -810,10 +810,10 @@
         <v>Là luồng xử lý riêng biệt chuyên dùng để vẽ giao diện đồ họa cho màn hình LCD — luồng đồ họa LCD</v>
       </c>
       <c r="H14" t="str">
-        <v>Là task tự động xóa toàn bộ các tệp tin log rác lưu trữ trên bộ nhớ ngoài Flash — dọn dẹp bộ nhớ Flash</v>
+        <v>Là task tự động chạy khi không có task nào khác ở trạng thái Ready, thường dùng để đưa chip vào chế độ tiết kiệm năng lượng (Low-power/Sleep) — chạy khi rảnh tiết kiệm điện năng</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -833,13 +833,13 @@
         <v>Task 1 giữ tài nguyên A và đợi tài nguyên B; Task 2 giữ tài nguyên B và đợi tài nguyên A; cả hai đều bị block vô hạn để đợi nhau — giữ tài nguyên đợi chéo lẫn nhau</v>
       </c>
       <c r="F15" t="str">
+        <v>Bộ dao động thạch anh ngoại vi của vi điều khiển bị hỏng vật lý khiến chip dừng chạy — hỏng thạch anh ngoại vi</v>
+      </c>
+      <c r="G15" t="str">
         <v>Vi điều khiển bị mất kết nối hoàn toàn với mạch nạp và không thể nạp lại code được nữa — mất kết nối mạch nạp</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>Mã nguồn chương trình C nhúng bị khai báo trùng lặp tên biến toàn cục trong nhiều file — trùng lặp tên biến</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Bộ dao động thạch anh ngoại vi của vi điều khiển bị hỏng vật lý khiến chip dừng chạy — hỏng thạch anh ngoại vi</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -859,19 +859,19 @@
         <v>Queue được cấp phát tĩnh hoặc động trong RAM dựa trên tích: Queue Length * Item Size. Cần khai báo Item Size chính xác (ví dụ `sizeof(DataStruct)`) để tránh lỗi ghi đè tràn bộ nhớ.</v>
       </c>
       <c r="E16" t="str">
+        <v>Queue Length: Độ dài tính bằng milimét của đường dây bus truyền dữ liệu — độ dài dây bus</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Item Size: Độ lớn vật lý của con chip vi điều khiển khi hàn lên bảng mạch — kích thước vật lý chip</v>
+      </c>
+      <c r="G16" t="str">
         <v>Queue Length: Số lượng phần tử tối đa hàng đợi có thể chứa; Item Size: Kích thước tính bằng byte của mỗi phần tử đó — số lượng phần tử tối đa và kích thước byte mỗi phần tử</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Queue Length: Độ dài tính bằng milimét của đường dây bus truyền dữ liệu — độ dài dây bus</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Item Size: Độ lớn vật lý của con chip vi điều khiển khi hàn lên bảng mạch — kích thước vật lý chip</v>
       </c>
       <c r="H16" t="str">
         <v>Queue Length: Tổng số lượng task đang lắng nghe hàng đợi đó cùng một lúc — số lượng task lắng nghe</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Preemptive là cơ chế lập lịch phổ biến nhất trong RTOS. Nó đảm bảo tính phản hồi nhanh của hệ thống đối với các sự kiện khẩn cấp. Khác với Cooperative Scheduling (lập lịch hợp tác, task tự nhường CPU).</v>
       </c>
       <c r="E17" t="str">
+        <v>Các task tự nguyện chia sẻ CPU bằng cách tự gọi hàm nhường quyền khi chạy xong một chu trình — chia sẻ tự nguyện hợp tác</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Hệ điều hành chia đều thời gian chạy CPU (Time-slice) cho tất cả các task bất kể độ ưu tiên của chúng — chia đều thời gian CPU</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Task nào được tạo ra đầu tiên trong hàm main() sẽ được chạy liên tục cho đến khi kết thúc dự án — chạy tuần tự tạo trước</v>
+      </c>
+      <c r="H17" t="str">
         <v>Khi một task có độ ưu tiên cao hơn chuyển sang trạng thái Ready, nó sẽ lập tức ngắt (cướp quyền) task có độ ưu tiên thấp hơn đang chạy để chiếm CPU — cướp quyền CPU dựa trên độ ưu tiên</v>
       </c>
-      <c r="F17" t="str">
-        <v>Các task tự nguyện chia sẻ CPU bằng cách tự gọi hàm nhường quyền khi chạy xong một chu trình — chia sẻ tự nguyện hợp tác</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Hệ điều hành chia đều thời gian chạy CPU (Time-slice) cho tất cả các task bất kể độ ưu tiên của chúng — chia đều thời gian CPU</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Task nào được tạo ra đầu tiên trong hàm main() sẽ được chạy liên tục cho đến khi kết thúc dự án — chạy tuần tự tạo trước</v>
-      </c>
       <c r="I17">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -946,19 +946,19 @@
         <v>Trong kiến trúc ARM Cortex-M, độ ưu tiên ngắt nhỏ hơn nghĩa là ưu tiên cao hơn. FreeRTOS định nghĩa `configMAX_SYSCALL_INTERRUPT_PRIORITY` (ngưỡng ngắt an toàn hệ điều hành). Các ngắt phần cứng có ưu tiên cao hơn ngưỡng này không bị RTOS trì hoãn (đáp ứng cực nhanh), nhưng tuyệt đối không được gọi bất kỳ API RTOS nào vì chúng không được bảo vệ bởi critical sections của RTOS, gây hỏng cấu trúc dữ liệu kernel dẫn đến HardFault.</v>
       </c>
       <c r="E19" t="str">
+        <v>Hàm `xQueueSendFromISR` bắt buộc phải được gọi bằng ngôn ngữ lập trình Assembly thay vì C nhúng — giới hạn ngôn ngữ gọi API</v>
+      </c>
+      <c r="F19" t="str">
+        <v>FreeRTOS cấm tuyệt đối việc gửi bất kỳ bản tin nào từ ngắt vào Message Queue — cấm gửi tin nhắn từ ngắt</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Ngắt UART sử dụng chung một thanh ghi dịch dữ liệu với cổng nạp SWD của chip — trùng lặp thanh ghi ngoại vi</v>
+      </c>
+      <c r="H19" t="str">
         <v>Ngắt UART được cấu hình độ ưu tiên phần cứng cao hơn (giá trị priority nhỏ hơn) so với cấu hình `configMAX_SYSCALL_INTERRUPT_PRIORITY` của FreeRTOS, dẫn đến việc gọi API RTOS từ ngắt bị cấm — phân quyền ngắt phần cứng vượt ngưỡng syscall</v>
       </c>
-      <c r="F19" t="str">
-        <v>Ngắt UART sử dụng chung một thanh ghi dịch dữ liệu với cổng nạp SWD của chip — trùng lặp thanh ghi ngoại vi</v>
-      </c>
-      <c r="G19" t="str">
-        <v>FreeRTOS cấm tuyệt đối việc gửi bất kỳ bản tin nào từ ngắt vào Message Queue — cấm gửi tin nhắn từ ngắt</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Hàm `xQueueSendFromISR` bắt buộc phải được gọi bằng ngôn ngữ lập trình Assembly thay vì C nhúng — giới hạn ngôn ngữ gọi API</v>
-      </c>
       <c r="I19">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -978,13 +978,13 @@
         <v>Đưa toàn bộ thuật toán điều khiển động cơ vào chạy trực tiếp trong một Timer Interrupt phần cứng có độ ưu tiên cao nhất, chỉ đẩy dữ liệu trạng thái qua DMA/Queue về RTOS task để xử lý giám sát và hiển thị sau — tách biệt luồng điều khiển cứng vào ngắt phần cứng</v>
       </c>
       <c r="F20" t="str">
+        <v>Tăng tần số xung nhịp hệ thống (SysTick Rate) của RTOS lên mức 100 kHz để tăng độ chính xác của scheduler — tăng SysTick rate quá tải CPU</v>
+      </c>
+      <c r="G20" t="str">
         <v>Tạo một RTOS task có độ ưu tiên cao nhất và sử dụng hàm `vTaskDelay(1)` để định thời chu kỳ điều khiển động cơ — định thời task RTOS rủi ro trễ</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Chạy hệ thống ở chế độ Cooperative Scheduling để các task tự chia sẻ CPU một cách hoàn hảo — cooperative scheduling không đảm bảo</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Tăng tần số xung nhịp hệ thống (SysTick Rate) của RTOS lên mức 100 kHz để tăng độ chính xác của scheduler — tăng SysTick rate quá tải CPU</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1007,10 +1007,10 @@
         <v>Gán cho mỗi tài nguyên dùng chung một độ ưu tiên trần (bằng độ ưu tiên cao nhất của task có thể dùng nó). Khi một task giữ khóa tài nguyên, nó tự động được nâng độ ưu tiên lên bằng độ ưu tiên trần này — nâng độ ưu tiên lên mức trần tài nguyên</v>
       </c>
       <c r="F21" t="str">
+        <v>Cấu hình cho hệ điều hành tự động chạy lại từ đầu khi phát hiện có tranh chấp tài nguyên xảy ra — tự động reset hệ thống</v>
+      </c>
+      <c r="G21" t="str">
         <v>Ngăn chặn hoàn toàn việc các task có độ ưu tiên khác nhau được phép truy cập vào cùng một tài nguyên — ngăn chặn truy cập chéo</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Cấu hình cho hệ điều hành tự động chạy lại từ đầu khi phát hiện có tranh chấp tài nguyên xảy ra — tự động reset hệ thống</v>
       </c>
       <c r="H21" t="str">
         <v>Yêu cầu lập trình viên không được phép sử dụng bất kỳ từ khóa Mutex hay Semaphore nào trong code — cấm dùng khóa</v>
@@ -1033,19 +1033,19 @@
         <v>`heap_1.c` chỉ cho malloc không cho free (thích hợp hệ thống khởi tạo 1 lần). `heap_2.c` cho free nhưng không ghép các khối trống nhỏ cạnh nhau lại thành khối lớn, chạy lâu năm sẽ bị phân mảnh (Fragmentation) dẫn đến việc `pvPortMalloc` báo lỗi hết bộ nhớ dù tổng RAM trống vẫn đủ. `heap_4.c` giải quyết triệt để bằng cách gộp các khối trống liền kề.</v>
       </c>
       <c r="E22" t="str">
+        <v>Vì `heap_4.c` hoàn toàn miễn phí còn các file heap khác bắt buộc phải mua bản quyền thương mại — bản quyền file heap</v>
+      </c>
+      <c r="F22" t="str">
         <v>Vì `heap_4.c` áp dụng thuật toán ghép các khối bộ nhớ trống kề nhau (Coalescing) để ngăn chặn hiện tượng phân mảnh bộ nhớ (Memory Fragmentation); `heap_1.c` không cho phép giải phóng, `heap_2.c` giải phóng nhưng không ghép khối — chống phân mảnh bộ nhớ ghép khối kề nhau</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
+        <v>Vì `heap_4.c` chỉ chạy được trên các dòng vi điều khiển ARM Cortex-M4 — giới hạn dòng chip</v>
+      </c>
+      <c r="H22" t="str">
         <v>Vì `heap_4.c` tự động nén dữ liệu lưu trên RAM sang bộ nhớ Flash khi tắt nguồn điện — nén dữ liệu Flash</v>
       </c>
-      <c r="G22" t="str">
-        <v>Vì `heap_4.c` hoàn toàn miễn phí còn các file heap khác bắt buộc phải mua bản quyền thương mại — bản quyền file heap</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Vì `heap_4.c` chỉ chạy được trên các dòng vi điều khiển ARM Cortex-M4 — giới hạn dòng chip</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Mặc định, ngắt SysTick xảy ra sau mỗi 1ms để cập nhật RTOS tick, điều này liên tục đánh thức chip dậy khỏi chế độ ngủ (Sleep Mode), gây hao pin. Tickless Idle tính toán xem task Ready tiếp theo sẽ chạy sau bao lâu (ví dụ 50ms nữa), sau đó cấu hình bộ hẹn giờ đánh thức và tắt ngắt SysTick, cho phép chip ngủ sâu liên tục trong 50ms.</v>
       </c>
       <c r="E23" t="str">
+        <v>Hệ điều hành tự động ngắt kết nối nguồn điện cấp cho toàn bộ các thiết bị ngoại vi cảm biến bên ngoài chip — ngắt nguồn ngoại vi</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Hệ điều hành bắt buộc lập trình viên phải rút mạch nạp chương trình ra khỏi chip khi đang chạy — rút mạch nạp</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Hệ điều hành tự động giảm tần số hoạt động của thạch anh ngoại vi xuống còn 1 Hz — giảm tần số thạch anh ngoại vi</v>
+      </c>
+      <c r="H23" t="str">
         <v>Hệ điều hành tạm thời dừng ngắt SysTick phần cứng khi hệ thống rảnh rỗi, cấu hình Timer phần cứng để đánh thức chip sau một khoảng thời gian dài ngủ sâu tương ứng với thời gian rảnh dự kiến — tắt ngắt SysTick định thời ngủ sâu</v>
       </c>
-      <c r="F23" t="str">
-        <v>Hệ điều hành tự động giảm tần số hoạt động của thạch anh ngoại vi xuống còn 1 Hz — giảm tần số thạch anh ngoại vi</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Hệ điều hành tự động ngắt kết nối nguồn điện cấp cho toàn bộ các thiết bị ngoại vi cảm biến bên ngoài chip — ngắt nguồn ngoại vi</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Hệ điều hành bắt buộc lập trình viên phải rút mạch nạp chương trình ra khỏi chip khi đang chạy — rút mạch nạp</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Task Notifications gửi tín hiệu trực tiếp vào TCB (Task Control Block) của task đích, chạy cực nhanh và không tốn RAM khởi tạo đối tượng độc lập. Event Groups là công cụ đồng bộ hóa mạnh mẽ, cho phép một task bị block cho đến khi toàn bộ các sự kiện mong muốn xảy ra (ví dụ: Task chỉ chạy khi cả 3 sự kiện Wifi connected AND Sensor read AND Flash ready đều tích cờ).</v>
       </c>
       <c r="E24" t="str">
+        <v>Task Notifications chỉ dùng cho dữ liệu số nguyên; còn Event Groups chỉ dùng cho kiểu dữ liệu chuỗi — kiểu dữ liệu truyền</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Task Notifications bắt buộc phải viết bằng ngôn ngữ Assembly; còn Event Groups viết bằng ngôn ngữ C — giới hạn ngôn ngữ code</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Task Notifications chỉ chạy trên môi trường giả lập; còn Event Groups chạy trên chip thực tế — phân loại môi trường chạy</v>
+      </c>
+      <c r="H24" t="str">
         <v>Task Notifications truyền tín hiệu trực tiếp đến một task cụ thể (nhanh hơn, tốn ít RAM hơn); Event Groups cho phép đồng bộ hóa nhiều task dựa trên tổ hợp nhiều sự kiện (AND/OR logic) — signaling đơn mục tiêu vs đồng bộ hóa đa sự kiện phức tạp</v>
       </c>
-      <c r="F24" t="str">
-        <v>Task Notifications chỉ dùng cho dữ liệu số nguyên; còn Event Groups chỉ dùng cho kiểu dữ liệu chuỗi — kiểu dữ liệu truyền</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Task Notifications bắt buộc phải viết bằng ngôn ngữ Assembly; còn Event Groups viết bằng ngôn ngữ C — giới hạn ngôn ngữ code</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Task Notifications chỉ chạy trên môi trường giả lập; còn Event Groups chạy trên chip thực tế — phân loại môi trường chạy</v>
-      </c>
       <c r="I24">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Trong kiến trúc ARM Cortex-M, FreeRTOS sử dụng thanh ghi `BASEPRI` để che (mask) các ngắt có độ ưu tiên thấp hơn SysTick khi chạy critical sections. Lỗi treo ở `vPortRaiseBASEPRI` thường do cấu hình sai nhóm ưu tiên ngắt (`NVIC_PriorityGroupConfig(NVIC_PriorityGroup_4)` không được gọi), dẫn đến việc tính toán mức ưu tiên của RTOS bị sai lệch gây lỗi Assert treo chip.</v>
       </c>
       <c r="E25" t="str">
+        <v>Đường dây bus truyền dữ liệu I2C ngoại vi bị chập mạch vật lý xuống đất — chập dây bus phần cứng</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Cầu chì bảo vệ chống đọc mã nguồn của con chip vi điều khiển đã bị kích hoạt — bảo vệ chống đọc code</v>
+      </c>
+      <c r="G25" t="str">
         <v>Hệ thống bị treo do một ngắt có priority cao hơn SysTick gọi một API RTOS thông thường hoặc xảy ra xung đột cấu hình phân nhóm ưu tiên ngắt (Priority Grouping) trên ARM Cortex-M — xung đột cấu hình priority grouping ngắt</v>
       </c>
-      <c r="F25" t="str">
+      <c r="H25" t="str">
         <v>Vi điều khiển bị hết dung lượng bộ nhớ Flash để lưu trữ mã nguồn chương trình — hết bộ nhớ Flash</v>
       </c>
-      <c r="G25" t="str">
-        <v>Cầu chì bảo vệ chống đọc mã nguồn của con chip vi điều khiển đã bị kích hoạt — bảo vệ chống đọc code</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Đường dây bus truyền dữ liệu I2C ngoại vi bị chập mạch vật lý xuống đất — chập dây bus phần cứng</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Trong các hệ thống y tế/hàng không, tính xác định (Determinism) là tuyệt đối. Việc malloc bộ nhớ động lúc đang chạy có thể thất bại nếu heap bị phân mảnh. Sử dụng các API `Static` (như `xTaskCreateStatic`, `xQueueCreateStatic`) yêu cầu lập trình viên khai báo sẵn vùng đệm buffer tĩnh (static arrays) từ trước, bộ nhớ được cấp phát và kiểm tra an toàn ngay khi biên dịch (compile-time), triệt tiêu rủi ro thiếu RAM lúc chạy.</v>
       </c>
       <c r="E26" t="str">
+        <v>Vì cấp phát tĩnh làm cho vi điều khiển hoạt động nóng hơn gấp đôi so với cấp phát động — sinh nhiệt phần cứng</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Vì chuẩn MISRA C cấm tuyệt đối việc sử dụng bất kỳ hàng đợi Message Queue nào trong lập trình nhúng — cấm sử dụng hàng đợi</v>
+      </c>
+      <c r="G26" t="str">
         <v>Vì cấp phát động tại Runtime có rủi ro cạn kiệt bộ nhớ Heap (Out-of-memory) hoặc phân mảnh bộ nhớ dẫn đến sập hệ thống bất ngờ; Giải pháp: Sử dụng các API cấp phát tĩnh (như `xQueueCreateStatic()`) tại thời điểm biên dịch — cấp phát tĩnh an toàn MISRA C</v>
       </c>
-      <c r="F26" t="str">
-        <v>Vì cấp phát tĩnh làm cho vi điều khiển hoạt động nóng hơn gấp đôi so với cấp phát động — sinh nhiệt phần cứng</v>
-      </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>Vì cấp phát tĩnh bắt buộc phải sử dụng nguồn điện pin 9V thay vì nguồn USB 5V — ràng buộc nguồn điện vật lý</v>
       </c>
-      <c r="H26" t="str">
-        <v>Vì chuẩn MISRA C cấm tuyệt đối việc sử dụng bất kỳ hàng đợi Message Queue nào trong lập trình nhúng — cấm sử dụng hàng đợi</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
